--- a/data/trans_dic/IP37-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP37-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han trabajado anteriormente</t>
+          <t>Adultos que han trabajado anteriormente (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>48,92; 83,48</t>
+          <t>48,61; 85,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70,21; 94,81</t>
+          <t>72,15; 95,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74,73; 95,17</t>
+          <t>76,6; 95,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59,49; 95,15</t>
+          <t>57,69; 95,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>60,2; 88,87</t>
+          <t>60,16; 90,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,18; 95,0</t>
+          <t>72,44; 94,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,82; 80,82</t>
+          <t>54,62; 82,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>58,58; 89,73</t>
+          <t>56,3; 89,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>60,66; 83,9</t>
+          <t>61,83; 83,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78,16; 93,4</t>
+          <t>78,78; 93,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69,35; 86,2</t>
+          <t>68,53; 86,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,59; 88,2</t>
+          <t>66,19; 89,1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>46,06; 66,72</t>
+          <t>45,79; 66,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,71; 73,39</t>
+          <t>51,27; 72,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53,01; 72,57</t>
+          <t>54,63; 73,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63,03; 94,91</t>
+          <t>63,49; 94,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,89; 58,03</t>
+          <t>34,22; 57,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,81; 70,81</t>
+          <t>51,39; 69,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,24; 73,63</t>
+          <t>56,13; 74,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>58,83; 82,33</t>
+          <t>57,24; 80,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44,1; 59,53</t>
+          <t>44,2; 58,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56,01; 69,93</t>
+          <t>55,26; 69,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58,19; 70,99</t>
+          <t>57,47; 71,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>65,71; 88,2</t>
+          <t>66,46; 88,26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,62; 68,57</t>
+          <t>36,97; 70,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,05; 81,64</t>
+          <t>60,19; 82,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69,34; 93,16</t>
+          <t>72,18; 93,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58,81; 88,81</t>
+          <t>58,89; 88,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>61,12; 85,52</t>
+          <t>62,41; 85,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56,86; 79,72</t>
+          <t>57,69; 79,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,19; 93,08</t>
+          <t>69,36; 92,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53,94; 83,17</t>
+          <t>50,18; 82,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>55,21; 75,73</t>
+          <t>55,15; 74,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63,1; 78,9</t>
+          <t>62,72; 78,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>75,26; 90,85</t>
+          <t>75,37; 90,92</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>61,21; 81,61</t>
+          <t>61,25; 83,02</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,88; 86,31</t>
+          <t>60,78; 85,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>72,15; 90,99</t>
+          <t>72,94; 91,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71,49; 93,01</t>
+          <t>72,03; 93,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38,73; 77,0</t>
+          <t>38,92; 76,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>61,64; 87,07</t>
+          <t>57,21; 85,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,97; 93,67</t>
+          <t>74,05; 93,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,86; 93,53</t>
+          <t>75,84; 93,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,45; 87,41</t>
+          <t>39,29; 87,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64,63; 83,44</t>
+          <t>64,51; 82,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77,93; 90,63</t>
+          <t>77,61; 91,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78,98; 91,39</t>
+          <t>78,08; 91,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46,04; 76,22</t>
+          <t>45,38; 75,57</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>46,41; 77,87</t>
+          <t>45,23; 78,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,04; 92,24</t>
+          <t>66,84; 92,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70,85; 93,56</t>
+          <t>69,17; 93,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,37; 85,57</t>
+          <t>14,73; 87,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>61,83; 92,91</t>
+          <t>62,1; 92,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,42; 81,64</t>
+          <t>50,54; 81,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,47; 97,53</t>
+          <t>80,63; 97,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,32; 75,8</t>
+          <t>20,41; 75,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57,51; 80,83</t>
+          <t>57,71; 82,19</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64,91; 84,26</t>
+          <t>64,59; 84,19</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78,86; 94,16</t>
+          <t>79,83; 94,48</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,29; 68,95</t>
+          <t>25,2; 67,78</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,69; 69,76</t>
+          <t>38,47; 71,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>59,15; 84,98</t>
+          <t>58,08; 84,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38,05; 69,61</t>
+          <t>38,01; 68,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54,43; 82,78</t>
+          <t>56,72; 83,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,75; 67,09</t>
+          <t>35,0; 67,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45,96; 73,16</t>
+          <t>46,69; 71,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,4; 50,9</t>
+          <t>19,38; 52,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59,2; 87,78</t>
+          <t>57,57; 87,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41,47; 64,25</t>
+          <t>41,47; 64,03</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>56,78; 76,51</t>
+          <t>56,78; 75,86</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32,77; 55,52</t>
+          <t>32,6; 56,04</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>62,04; 82,3</t>
+          <t>63,38; 82,57</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>53,33; 72,85</t>
+          <t>52,74; 74,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>74,22; 88,57</t>
+          <t>73,99; 88,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51,94; 73,53</t>
+          <t>51,61; 73,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62,27; 88,08</t>
+          <t>61,62; 86,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>53,0; 71,86</t>
+          <t>52,49; 71,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,1; 82,13</t>
+          <t>65,95; 83,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,34; 78,84</t>
+          <t>58,49; 78,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>73,96; 93,89</t>
+          <t>72,89; 93,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>56,09; 69,93</t>
+          <t>56,55; 70,03</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72,46; 83,3</t>
+          <t>72,69; 83,76</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59,12; 74,95</t>
+          <t>58,32; 72,84</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>71,68; 88,47</t>
+          <t>71,5; 87,7</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>49,91; 68,81</t>
+          <t>50,24; 68,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>67,63; 83,26</t>
+          <t>67,61; 83,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>80,31; 92,54</t>
+          <t>80,72; 92,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36,81; 60,39</t>
+          <t>36,31; 59,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>53,47; 71,73</t>
+          <t>53,07; 71,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,09; 86,44</t>
+          <t>71,27; 86,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,74; 86,49</t>
+          <t>70,97; 86,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>43,16; 68,96</t>
+          <t>43,43; 68,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>53,5; 67,03</t>
+          <t>54,19; 67,47</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72,06; 82,79</t>
+          <t>71,67; 82,78</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78,33; 87,87</t>
+          <t>78,27; 88,2</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>43,93; 60,97</t>
+          <t>43,13; 60,7</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>56,86; 66,29</t>
+          <t>56,54; 65,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>73,46; 80,34</t>
+          <t>73,19; 80,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>72,36; 79,79</t>
+          <t>72,55; 79,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>63,64; 79,49</t>
+          <t>63,07; 79,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>58,76; 67,42</t>
+          <t>59,07; 67,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>69,75; 76,96</t>
+          <t>69,99; 76,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>69,34; 76,82</t>
+          <t>69,66; 77,22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>64,93; 75,68</t>
+          <t>63,54; 75,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>58,98; 65,36</t>
+          <t>59,08; 65,36</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72,56; 77,35</t>
+          <t>72,26; 77,52</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72,04; 77,25</t>
+          <t>72,01; 77,31</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>65,78; 75,57</t>
+          <t>65,86; 75,95</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han trabajado anteriormente (tasa de respuesta: 99,71%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>11262</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28506</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>27201</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22802</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>18833</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>29580</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>22166</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>17425</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>30094</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>58086</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>49367</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>40228</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>8059; 14140</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>23784; 31415</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>23690; 29475</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15976; 26363</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>14400; 21748</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>24511; 32029</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>17541; 26335</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>12967; 20540</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>25050; 33980</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>52628; 62542</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>43206; 54410</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>33575; 45195</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>32962</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>34496</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>42513</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>56011</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>23803</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>44789</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>47739</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>42066</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>56765</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>79286</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>90252</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98077</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>26656; 38918</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>27982; 39814</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>36384; 49055</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>44407; 66109</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>17644; 29764</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>37331; 50791</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>41297; 54483</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>33951; 47811</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>48518; 64677</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>70307; 89022</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>80553; 99568</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>85907; 114080</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>13733</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>31615</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>29941</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>15603</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>22427</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>30895</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>25563</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>18942</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>62510</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>55504</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>34545</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>9428; 17971</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>26425; 36136</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>25552; 33092</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11963; 18034</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>18657; 25593</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>25549; 35046</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>21196; 28409</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>13797; 22734</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>30553; 41474</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>55309; 69526</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>49713; 59966</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>29279; 39690</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>21746</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>34813</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>37234</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14607</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>18832</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>36497</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>41764</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>11506</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>40578</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>71309</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>78998</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>26113</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>17611; 24892</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>30329; 38216</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>31449; 40682</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>9600; 18901</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>14455; 21645</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>31290; 39649</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>36392; 45007</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>6909; 15353</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>34987; 44903</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>65065; 76433</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>71554; 84002</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>19176; 31930</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>14139</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23628</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>23970</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>16150</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>18746</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>22855</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3311</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>30290</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>42374</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>46825</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>5025</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>10192; 17593</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>19189; 26576</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>19554; 26353</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>531; 3144</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>12646; 18918</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>13899; 22484</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>19987; 24175</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1445; 5324</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>24755; 35257</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>36308; 47326</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>42357; 50129</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2694; 7245</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>13307</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>25939</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>14914</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>16797</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>12031</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>22314</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>8601</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>15929</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>25338</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>48253</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>23515</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>32726</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>9263; 17229</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>20304; 29657</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>10627; 19034</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>13401; 19660</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>8238; 15849</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>17355; 26673</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>4902; 13315</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>12081; 18319</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>19749; 30490</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>40956; 54714</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>17362; 29841</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>28277; 36837</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>37294</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>63497</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>31212</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>29250</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>45695</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>60191</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>38278</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>40782</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>82989</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>123688</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>69491</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>70033</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>31025; 43537</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>57147; 68436</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>25621; 36456</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>23751; 33384</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>38411; 52537</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>52828; 66504</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>32263; 43368</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>34744; 44585</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>74655; 92447</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>114373; 131781</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>61116; 76339</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>61637; 75601</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>39857</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>57063</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>69828</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>23672</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>43227</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>61211</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>61509</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>30003</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>83085</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>118273</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>131337</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>53675</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>33544; 45987</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>50820; 62410</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>64475; 74220</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>17882; 29454</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>36727; 49288</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>54798; 66187</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>54897; 66554</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>23133; 36246</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>73690; 91741</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>108977; 125874</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>123070; 138687</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>44210; 62228</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>184301</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>299556</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>276814</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>180457</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>200999</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>304222</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>268476</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>179964</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>385300</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>603778</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>545289</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>360421</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>170456; 197088</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>284784; 312239</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>262856; 288726</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>162495; 204839</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>187220; 214065</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>290227; 317646</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>255559; 283291</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>162932; 192773</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>365387; 404206</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>580782; 623064</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>525049; 563719</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>338564; 390416</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP37-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP37-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>48,61; 85,28</t>
+          <t>45,41; 82,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72,15; 95,29</t>
+          <t>72,09; 95,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,6; 95,3</t>
+          <t>76,76; 95,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57,69; 95,19</t>
+          <t>57,86; 95,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>60,16; 90,86</t>
+          <t>60,83; 90,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,44; 94,66</t>
+          <t>75,41; 95,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,62; 82,0</t>
+          <t>51,99; 79,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56,3; 89,19</t>
+          <t>55,72; 88,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>61,83; 83,87</t>
+          <t>61,32; 83,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78,78; 93,62</t>
+          <t>78,12; 93,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68,53; 86,31</t>
+          <t>69,38; 86,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,19; 89,1</t>
+          <t>65,68; 90,4</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>45,79; 66,85</t>
+          <t>45,26; 66,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,27; 72,95</t>
+          <t>51,57; 73,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54,63; 73,65</t>
+          <t>52,78; 73,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63,49; 94,52</t>
+          <t>63,4; 93,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,22; 57,72</t>
+          <t>34,91; 57,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,39; 69,91</t>
+          <t>52,88; 70,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,13; 74,05</t>
+          <t>55,91; 73,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>57,24; 80,6</t>
+          <t>59,08; 81,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44,2; 58,92</t>
+          <t>44,64; 59,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55,26; 69,97</t>
+          <t>54,84; 68,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57,47; 71,03</t>
+          <t>57,08; 70,39</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>66,46; 88,26</t>
+          <t>66,3; 88,13</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,97; 70,47</t>
+          <t>36,61; 71,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,19; 82,31</t>
+          <t>59,29; 82,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72,18; 93,48</t>
+          <t>72,64; 93,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58,89; 88,77</t>
+          <t>59,74; 88,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62,41; 85,61</t>
+          <t>62,42; 85,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>57,69; 79,14</t>
+          <t>56,4; 79,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,36; 92,96</t>
+          <t>70,68; 92,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50,18; 82,69</t>
+          <t>52,37; 80,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>55,15; 74,86</t>
+          <t>54,32; 75,88</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62,72; 78,84</t>
+          <t>61,72; 78,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>75,37; 90,92</t>
+          <t>75,31; 90,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>61,25; 83,02</t>
+          <t>61,4; 81,83</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>60,78; 85,91</t>
+          <t>60,41; 86,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>72,94; 91,91</t>
+          <t>73,38; 91,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72,03; 93,18</t>
+          <t>73,64; 93,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38,92; 76,62</t>
+          <t>39,38; 78,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,21; 85,68</t>
+          <t>60,35; 87,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,05; 93,84</t>
+          <t>73,6; 93,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,84; 93,79</t>
+          <t>75,07; 94,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,29; 87,31</t>
+          <t>38,89; 87,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64,51; 82,79</t>
+          <t>65,6; 83,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77,61; 91,17</t>
+          <t>77,01; 90,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78,08; 91,66</t>
+          <t>79,45; 92,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45,38; 75,57</t>
+          <t>47,61; 77,07</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>45,23; 78,08</t>
+          <t>44,85; 78,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>66,84; 92,56</t>
+          <t>67,29; 91,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,17; 93,22</t>
+          <t>69,28; 93,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,73; 87,14</t>
+          <t>11,78; 86,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>62,1; 92,91</t>
+          <t>61,64; 92,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,54; 81,76</t>
+          <t>52,62; 81,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,63; 97,52</t>
+          <t>79,1; 97,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,41; 75,18</t>
+          <t>21,71; 75,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57,71; 82,19</t>
+          <t>57,83; 81,44</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64,59; 84,19</t>
+          <t>62,99; 84,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79,83; 94,48</t>
+          <t>79,02; 94,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,2; 67,78</t>
+          <t>26,2; 68,27</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38,47; 71,55</t>
+          <t>38,77; 71,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>58,08; 84,83</t>
+          <t>60,84; 84,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38,01; 68,08</t>
+          <t>38,09; 68,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56,72; 83,21</t>
+          <t>54,66; 83,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35,0; 67,33</t>
+          <t>36,35; 67,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46,69; 71,76</t>
+          <t>45,5; 71,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,38; 52,64</t>
+          <t>18,66; 53,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>57,57; 87,3</t>
+          <t>57,09; 88,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41,47; 64,03</t>
+          <t>40,5; 63,55</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>56,78; 75,86</t>
+          <t>56,78; 75,14</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32,6; 56,04</t>
+          <t>33,54; 55,46</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>63,38; 82,57</t>
+          <t>62,93; 82,73</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>52,74; 74,01</t>
+          <t>53,68; 74,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>73,99; 88,61</t>
+          <t>73,64; 88,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51,61; 73,44</t>
+          <t>51,06; 72,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61,62; 86,62</t>
+          <t>62,96; 86,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>52,49; 71,79</t>
+          <t>52,95; 71,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,95; 83,02</t>
+          <t>65,87; 82,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,49; 78,62</t>
+          <t>57,99; 79,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>72,89; 93,54</t>
+          <t>73,83; 94,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>56,55; 70,03</t>
+          <t>56,43; 69,49</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72,69; 83,76</t>
+          <t>72,99; 83,75</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58,32; 72,84</t>
+          <t>58,52; 73,62</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>71,5; 87,7</t>
+          <t>72,59; 88,55</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>50,24; 68,87</t>
+          <t>49,54; 68,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>67,61; 83,03</t>
+          <t>67,78; 83,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>80,72; 92,92</t>
+          <t>80,43; 92,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36,31; 59,81</t>
+          <t>35,42; 60,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>53,07; 71,22</t>
+          <t>52,22; 71,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,27; 86,08</t>
+          <t>71,85; 86,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,97; 86,04</t>
+          <t>70,98; 86,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>43,43; 68,04</t>
+          <t>43,41; 67,98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>54,19; 67,47</t>
+          <t>55,14; 67,95</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>71,67; 82,78</t>
+          <t>71,83; 83,13</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78,27; 88,2</t>
+          <t>77,79; 87,89</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>43,13; 60,7</t>
+          <t>43,88; 61,64</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>56,54; 65,37</t>
+          <t>56,86; 65,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>73,19; 80,25</t>
+          <t>73,15; 80,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>72,55; 79,69</t>
+          <t>72,64; 79,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>63,07; 79,5</t>
+          <t>63,53; 79,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>59,07; 67,54</t>
+          <t>59,33; 68,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>69,99; 76,6</t>
+          <t>69,4; 76,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>69,66; 77,22</t>
+          <t>69,4; 77,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>63,54; 75,18</t>
+          <t>64,27; 75,3</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>59,08; 65,36</t>
+          <t>59,25; 65,32</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72,26; 77,52</t>
+          <t>72,49; 77,57</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72,01; 77,31</t>
+          <t>72,23; 77,42</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>65,86; 75,95</t>
+          <t>65,95; 75,52</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8059; 14140</t>
+          <t>7530; 13636</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23784; 31415</t>
+          <t>23765; 31371</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23690; 29475</t>
+          <t>23740; 29535</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15976; 26363</t>
+          <t>16025; 26329</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14400; 21748</t>
+          <t>14561; 21721</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24511; 32029</t>
+          <t>25516; 32163</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17541; 26335</t>
+          <t>16698; 25650</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12967; 20540</t>
+          <t>12833; 20301</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25050; 33980</t>
+          <t>24847; 34017</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52628; 62542</t>
+          <t>52188; 62352</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43206; 54410</t>
+          <t>43741; 54348</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33575; 45195</t>
+          <t>33319; 45856</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26656; 38918</t>
+          <t>26350; 38937</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27982; 39814</t>
+          <t>28148; 40012</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36384; 49055</t>
+          <t>35155; 48754</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>44407; 66109</t>
+          <t>44344; 65624</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17644; 29764</t>
+          <t>18000; 29402</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37331; 50791</t>
+          <t>38419; 51437</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41297; 54483</t>
+          <t>41138; 53976</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33951; 47811</t>
+          <t>35042; 48495</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48518; 64677</t>
+          <t>49004; 65134</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>70307; 89022</t>
+          <t>69774; 87711</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>80553; 99568</t>
+          <t>80007; 98675</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>85907; 114080</t>
+          <t>85701; 113919</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9428; 17971</t>
+          <t>9336; 18107</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26425; 36136</t>
+          <t>26027; 36309</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25552; 33092</t>
+          <t>25715; 33087</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11963; 18034</t>
+          <t>12135; 18020</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18657; 25593</t>
+          <t>18661; 25578</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25549; 35046</t>
+          <t>24975; 35313</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21196; 28409</t>
+          <t>21600; 28403</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13797; 22734</t>
+          <t>14399; 22201</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30553; 41474</t>
+          <t>30091; 42037</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55309; 69526</t>
+          <t>54424; 69051</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49713; 59966</t>
+          <t>49674; 59721</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29279; 39690</t>
+          <t>29353; 39120</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17611; 24892</t>
+          <t>17505; 25032</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30329; 38216</t>
+          <t>30512; 37992</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31449; 40682</t>
+          <t>32148; 40631</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9600; 18901</t>
+          <t>9716; 19345</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14455; 21645</t>
+          <t>15246; 22027</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31290; 39649</t>
+          <t>31099; 39543</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36392; 45007</t>
+          <t>36024; 45136</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6909; 15353</t>
+          <t>6839; 15339</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34987; 44903</t>
+          <t>35581; 45539</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>65065; 76433</t>
+          <t>64557; 75867</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71554; 84002</t>
+          <t>72810; 84320</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19176; 31930</t>
+          <t>20116; 32563</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10192; 17593</t>
+          <t>10107; 17591</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19189; 26576</t>
+          <t>19320; 26356</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19554; 26353</t>
+          <t>19586; 26398</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>531; 3144</t>
+          <t>425; 3124</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12646; 18918</t>
+          <t>12553; 18929</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13899; 22484</t>
+          <t>14472; 22415</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19987; 24175</t>
+          <t>19610; 24190</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1445; 5324</t>
+          <t>1537; 5357</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24755; 35257</t>
+          <t>24808; 34933</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>36308; 47326</t>
+          <t>35411; 47362</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42357; 50129</t>
+          <t>41929; 49997</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2694; 7245</t>
+          <t>2800; 7297</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9263; 17229</t>
+          <t>9336; 17264</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20304; 29657</t>
+          <t>21270; 29697</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10627; 19034</t>
+          <t>10649; 19039</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13401; 19660</t>
+          <t>12914; 19684</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8238; 15849</t>
+          <t>8556; 15831</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17355; 26673</t>
+          <t>16913; 26729</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4902; 13315</t>
+          <t>4720; 13407</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12081; 18319</t>
+          <t>11980; 18552</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19749; 30490</t>
+          <t>19284; 30260</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>40956; 54714</t>
+          <t>40956; 54195</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17362; 29841</t>
+          <t>17860; 29530</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>28277; 36837</t>
+          <t>28073; 36910</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>31025; 43537</t>
+          <t>31580; 43552</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>57147; 68436</t>
+          <t>56870; 68298</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25621; 36456</t>
+          <t>25346; 36148</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23751; 33384</t>
+          <t>24266; 33417</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>38411; 52537</t>
+          <t>38749; 51996</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>52828; 66504</t>
+          <t>52763; 65834</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32263; 43368</t>
+          <t>31992; 43905</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>34744; 44585</t>
+          <t>35192; 44809</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>74655; 92447</t>
+          <t>74497; 91734</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>114373; 131781</t>
+          <t>114837; 131764</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>61116; 76339</t>
+          <t>61328; 77161</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>61637; 75601</t>
+          <t>62582; 76342</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>33544; 45987</t>
+          <t>33078; 45814</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>50820; 62410</t>
+          <t>50947; 62439</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>64475; 74220</t>
+          <t>64248; 73553</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17882; 29454</t>
+          <t>17445; 29557</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>36727; 49288</t>
+          <t>36138; 49261</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>54798; 66187</t>
+          <t>55251; 66269</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>54897; 66554</t>
+          <t>54911; 66725</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>23133; 36246</t>
+          <t>23123; 36215</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>73690; 91741</t>
+          <t>74976; 92392</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>108977; 125874</t>
+          <t>109227; 126402</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>123070; 138687</t>
+          <t>122314; 138188</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>44210; 62228</t>
+          <t>44981; 63194</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>170456; 197088</t>
+          <t>171440; 198509</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>284784; 312239</t>
+          <t>284619; 312540</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>262856; 288726</t>
+          <t>263178; 289108</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>162495; 204839</t>
+          <t>163670; 205255</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>187220; 214065</t>
+          <t>188033; 215929</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>290227; 317646</t>
+          <t>287798; 318138</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>255559; 283291</t>
+          <t>254604; 282717</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>162932; 192773</t>
+          <t>164795; 193078</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>365387; 404206</t>
+          <t>366403; 403945</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>580782; 623064</t>
+          <t>582699; 623538</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>525049; 563719</t>
+          <t>526669; 564503</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>338564; 390416</t>
+          <t>339051; 388210</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP37-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP37-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>78,68%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>87,42%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>69,02%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>75,94%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>67,92%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>86,47%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>87,95%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>82,34%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>78,68%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>87,42%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>69,02%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>78,66%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45,41; 82,24</t>
+          <t>60,2; 88,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72,09; 95,16</t>
+          <t>76,18; 95,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,76; 95,49</t>
+          <t>52,82; 80,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57,86; 95,07</t>
+          <t>57,42; 89,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>60,83; 90,74</t>
+          <t>48,92; 83,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,41; 95,06</t>
+          <t>70,21; 94,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,99; 79,87</t>
+          <t>74,73; 95,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>55,72; 88,15</t>
+          <t>64,32; 93,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>61,32; 83,96</t>
+          <t>60,66; 83,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78,12; 93,34</t>
+          <t>78,16; 93,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69,38; 86,21</t>
+          <t>69,35; 86,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,68; 90,4</t>
+          <t>66,51; 87,58</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>46,16%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>61,65%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64,88%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>69,35%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>56,62%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>63,21%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>63,83%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>80,08%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>46,16%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>61,65%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>64,88%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>68,92%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>45,26; 66,88</t>
+          <t>35,89; 58,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,57; 73,31</t>
+          <t>51,81; 70,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52,78; 73,2</t>
+          <t>55,24; 73,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63,4; 93,83</t>
+          <t>56,37; 81,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,91; 57,02</t>
+          <t>46,06; 66,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,88; 70,8</t>
+          <t>51,71; 73,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,91; 73,36</t>
+          <t>53,01; 72,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>59,08; 81,76</t>
+          <t>54,51; 79,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44,64; 59,33</t>
+          <t>44,1; 59,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54,84; 68,94</t>
+          <t>56,01; 69,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57,08; 70,39</t>
+          <t>58,19; 70,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>66,3; 88,13</t>
+          <t>59,78; 77,01</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>75,02%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>69,76%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>83,65%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>69,73%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>53,85%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>72,01%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>84,58%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>76,81%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>75,02%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>69,76%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>83,65%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,43%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,61; 71,0</t>
+          <t>61,12; 85,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,29; 82,71</t>
+          <t>56,86; 79,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72,64; 93,47</t>
+          <t>71,19; 93,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59,74; 88,71</t>
+          <t>55,25; 83,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62,42; 85,56</t>
+          <t>36,62; 68,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56,4; 79,74</t>
+          <t>60,05; 81,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,68; 92,94</t>
+          <t>69,34; 93,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52,37; 80,75</t>
+          <t>57,48; 88,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54,32; 75,88</t>
+          <t>55,21; 75,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61,72; 78,3</t>
+          <t>63,1; 78,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>75,31; 90,54</t>
+          <t>75,26; 90,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>61,4; 81,83</t>
+          <t>61,35; 81,55</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>74,54%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>86,38%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>87,03%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>67,07%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>75,05%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>83,72%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>85,28%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>59,21%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>74,54%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>86,38%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>87,03%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>62,02%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>60,41; 86,39</t>
+          <t>61,64; 87,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73,38; 91,37</t>
+          <t>73,97; 93,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,64; 93,06</t>
+          <t>74,86; 93,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39,38; 78,42</t>
+          <t>37,86; 88,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>60,35; 87,19</t>
+          <t>59,88; 86,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,6; 93,59</t>
+          <t>72,15; 90,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,07; 94,06</t>
+          <t>71,49; 93,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,89; 87,23</t>
+          <t>37,31; 76,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>65,6; 83,96</t>
+          <t>64,63; 83,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77,01; 90,5</t>
+          <t>77,93; 90,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79,45; 92,01</t>
+          <t>78,98; 91,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47,61; 77,07</t>
+          <t>46,12; 76,97</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>79,31%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>68,16%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>92,2%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>46,77%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>62,75%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>82,3%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>84,79%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>47,5%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>79,31%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>68,16%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>92,2%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,52%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>44,85; 78,07</t>
+          <t>61,83; 92,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67,29; 91,8</t>
+          <t>52,42; 81,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,28; 93,38</t>
+          <t>78,47; 97,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,78; 86,59</t>
+          <t>20,22; 75,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>61,64; 92,96</t>
+          <t>46,41; 77,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,62; 81,5</t>
+          <t>68,04; 92,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,1; 97,58</t>
+          <t>70,85; 93,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,71; 75,66</t>
+          <t>13,52; 83,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57,83; 81,44</t>
+          <t>57,51; 80,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62,99; 84,25</t>
+          <t>64,91; 84,26</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79,02; 94,23</t>
+          <t>78,86; 94,16</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,2; 68,27</t>
+          <t>25,76; 68,76</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>51,11%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>60,03%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>34,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>74,89%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>55,26%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>74,19%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>53,35%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>71,09%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>51,11%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>60,03%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>34,0%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>71,6%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38,77; 71,69</t>
+          <t>33,75; 67,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60,84; 84,95</t>
+          <t>45,96; 73,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38,09; 68,1</t>
+          <t>18,4; 50,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54,66; 83,31</t>
+          <t>57,34; 87,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36,35; 67,25</t>
+          <t>37,69; 69,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45,5; 71,91</t>
+          <t>59,15; 84,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,66; 53,0</t>
+          <t>38,05; 69,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>57,09; 88,41</t>
+          <t>51,87; 81,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40,5; 63,55</t>
+          <t>41,47; 64,25</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>56,78; 75,14</t>
+          <t>56,78; 76,51</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33,54; 55,46</t>
+          <t>32,77; 55,52</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>62,93; 82,73</t>
+          <t>59,8; 81,01</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>62,44%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>75,14%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>69,39%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>84,43%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>63,39%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>82,22%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>62,88%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>75,89%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>62,44%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>75,14%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>69,39%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>79,62%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>53,68; 74,03</t>
+          <t>53,0; 71,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>73,64; 88,43</t>
+          <t>65,1; 82,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51,06; 72,82</t>
+          <t>58,34; 78,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62,96; 86,7</t>
+          <t>72,84; 93,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>52,95; 71,05</t>
+          <t>53,33; 72,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,87; 82,18</t>
+          <t>74,22; 88,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,99; 79,59</t>
+          <t>51,94; 73,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>73,83; 94,01</t>
+          <t>60,19; 87,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>56,43; 69,49</t>
+          <t>56,09; 69,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72,99; 83,75</t>
+          <t>72,46; 83,3</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58,52; 73,62</t>
+          <t>59,12; 74,95</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>72,59; 88,55</t>
+          <t>70,75; 87,41</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>62,47%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>79,61%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>79,51%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>56,28%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>59,69%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>75,91%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>87,42%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>48,07%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>62,47%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>79,61%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>79,51%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,18%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>49,54; 68,61</t>
+          <t>53,47; 71,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>67,78; 83,06</t>
+          <t>71,09; 86,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>80,43; 92,08</t>
+          <t>71,74; 86,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35,42; 60,02</t>
+          <t>43,06; 68,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>52,22; 71,18</t>
+          <t>49,91; 68,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,85; 86,18</t>
+          <t>67,63; 83,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,98; 86,26</t>
+          <t>80,31; 92,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>43,41; 67,98</t>
+          <t>36,42; 60,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>55,14; 67,95</t>
+          <t>53,5; 67,03</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>71,83; 83,13</t>
+          <t>72,06; 82,79</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77,79; 87,89</t>
+          <t>78,33; 87,87</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>43,88; 61,64</t>
+          <t>42,97; 60,27</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>63,42%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>73,36%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>73,19%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>69,11%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>61,13%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>76,99%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>76,4%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>70,04%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>63,42%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>73,36%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>73,19%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>67,04%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>56,86; 65,84</t>
+          <t>58,76; 67,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>73,15; 80,32</t>
+          <t>69,75; 76,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>72,64; 79,79</t>
+          <t>69,34; 76,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>63,53; 79,67</t>
+          <t>63,97; 74,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>59,33; 68,13</t>
+          <t>56,86; 66,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>69,4; 76,72</t>
+          <t>73,46; 80,34</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>69,4; 77,07</t>
+          <t>72,36; 79,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>64,27; 75,3</t>
+          <t>58,93; 69,8</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>59,25; 65,32</t>
+          <t>58,98; 65,36</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72,49; 77,57</t>
+          <t>72,56; 77,35</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72,23; 77,42</t>
+          <t>72,04; 77,25</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>65,95; 75,52</t>
+          <t>63,26; 71,21</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>18833</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>29580</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>22166</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14302</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>11262</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>28506</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>27201</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>22802</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>18833</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>29580</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>22166</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17425</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40228</t>
+          <t>28301</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7530; 13636</t>
+          <t>14409; 21272</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23765; 31371</t>
+          <t>25777; 32144</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23740; 29535</t>
+          <t>16962; 25957</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16025; 26329</t>
+          <t>10814; 16814</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14561; 21721</t>
+          <t>8111; 13840</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25516; 32163</t>
+          <t>23145; 31256</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16698; 25650</t>
+          <t>23111; 29435</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12833; 20301</t>
+          <t>11030; 16058</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24847; 34017</t>
+          <t>24577; 33995</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52188; 62352</t>
+          <t>52216; 62395</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43741; 54348</t>
+          <t>43721; 54341</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33319; 45856</t>
+          <t>23929; 31512</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>23803</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>44789</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47739</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>37577</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>32962</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>34496</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>42513</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>56011</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>23803</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>44789</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>47739</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>42066</t>
+          <t>29697</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98077</t>
+          <t>67274</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26350; 38937</t>
+          <t>18508; 29920</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28148; 40012</t>
+          <t>37642; 51441</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35155; 48754</t>
+          <t>40646; 54177</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>44344; 65624</t>
+          <t>30544; 43907</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18000; 29402</t>
+          <t>26813; 38843</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38419; 51437</t>
+          <t>28222; 40055</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41138; 53976</t>
+          <t>35304; 48334</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35042; 48495</t>
+          <t>23672; 34697</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49004; 65134</t>
+          <t>48413; 65348</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69774; 87711</t>
+          <t>71254; 88964</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>80007; 98675</t>
+          <t>81564; 99508</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>85701; 113919</t>
+          <t>58350; 75171</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>22427</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>30895</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>25563</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>16686</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>13733</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>31615</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>29941</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>15603</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>22427</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>30895</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>25563</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18942</t>
+          <t>15361</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34545</t>
+          <t>32047</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9336; 18107</t>
+          <t>18273; 25565</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26027; 36309</t>
+          <t>25183; 35304</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25715; 33087</t>
+          <t>21756; 28444</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12135; 18020</t>
+          <t>13221; 19923</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18661; 25578</t>
+          <t>9338; 17487</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24975; 35313</t>
+          <t>26361; 35840</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21600; 28403</t>
+          <t>24547; 32977</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14399; 22201</t>
+          <t>11676; 17932</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30091; 42037</t>
+          <t>30584; 41955</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54424; 69051</t>
+          <t>55648; 69578</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49674; 59721</t>
+          <t>49641; 59925</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29353; 39120</t>
+          <t>27145; 36080</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>18832</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>36497</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>41764</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>11061</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>21746</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>34813</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>37234</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>14607</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>18832</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>36497</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>41764</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11506</t>
+          <t>14852</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26113</t>
+          <t>25913</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17505; 25032</t>
+          <t>15572; 21998</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30512; 37992</t>
+          <t>31253; 39579</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32148; 40631</t>
+          <t>35922; 44881</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9716; 19345</t>
+          <t>6245; 14517</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15246; 22027</t>
+          <t>17350; 25007</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31099; 39543</t>
+          <t>29999; 37833</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36024; 45136</t>
+          <t>31210; 40609</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6839; 15339</t>
+          <t>9436; 19440</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35581; 45539</t>
+          <t>35051; 45257</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64557; 75867</t>
+          <t>65335; 75982</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>72810; 84320</t>
+          <t>72382; 83750</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20116; 32563</t>
+          <t>19270; 32159</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>16150</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>18746</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>22855</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>14139</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>23628</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>23970</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>16150</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>18746</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>22855</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5006</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10107; 17591</t>
+          <t>12590; 18920</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19320; 26356</t>
+          <t>14416; 22454</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19586; 26398</t>
+          <t>19453; 24178</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>425; 3124</t>
+          <t>1427; 5328</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12553; 18929</t>
+          <t>10459; 17547</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14472; 22415</t>
+          <t>19534; 26482</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19610; 24190</t>
+          <t>20027; 26449</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1537; 5357</t>
+          <t>500; 3091</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24808; 34933</t>
+          <t>24668; 34671</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35411; 47362</t>
+          <t>36485; 47364</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41929; 49997</t>
+          <t>41844; 49959</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2800; 7297</t>
+          <t>2772; 7400</t>
         </is>
       </c>
     </row>
@@ -3118,37 +3118,37 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>12031</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>22314</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>8601</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>13810</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>13307</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>25939</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>14914</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>16797</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>12031</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>22314</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>8601</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>15929</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>32726</t>
+          <t>29798</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9336; 17264</t>
+          <t>7945; 15794</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21270; 29697</t>
+          <t>17084; 27193</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10649; 19039</t>
+          <t>4655; 12875</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12914; 19684</t>
+          <t>10574; 16080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8556; 15831</t>
+          <t>9076; 16799</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16913; 26729</t>
+          <t>20679; 29709</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4720; 13407</t>
+          <t>10638; 19461</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11980; 18552</t>
+          <t>12022; 18841</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19284; 30260</t>
+          <t>19747; 30597</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>40956; 54195</t>
+          <t>40953; 55182</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17860; 29530</t>
+          <t>17448; 29564</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>28073; 36910</t>
+          <t>24888; 33716</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>45695</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>60191</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>38278</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>34840</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>37294</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>63497</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>31212</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>29250</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>45695</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>60191</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>38278</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>40782</t>
+          <t>28024</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>70033</t>
+          <t>62865</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>31580; 43552</t>
+          <t>38782; 52589</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>56870; 68298</t>
+          <t>52150; 65790</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25346; 36148</t>
+          <t>32185; 43491</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24266; 33417</t>
+          <t>30056; 38501</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>38749; 51996</t>
+          <t>31373; 42855</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>52763; 65834</t>
+          <t>57321; 68400</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31992; 43905</t>
+          <t>25780; 36498</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>35192; 44809</t>
+          <t>22689; 32855</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>74497; 91734</t>
+          <t>74041; 92311</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>114837; 131764</t>
+          <t>114014; 131063</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>61328; 77161</t>
+          <t>61957; 78552</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>62582; 76342</t>
+          <t>55861; 69019</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>43227</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>61211</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>61509</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>30880</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>39857</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>57063</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>69828</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>23672</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>43227</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>61211</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>61509</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>30003</t>
+          <t>25059</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>53675</t>
+          <t>55938</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>33078; 45814</t>
+          <t>37000; 49635</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>50947; 62439</t>
+          <t>54663; 66467</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>64248; 73553</t>
+          <t>55498; 66904</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17445; 29557</t>
+          <t>23627; 37631</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>36138; 49261</t>
+          <t>33323; 45944</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>55251; 66269</t>
+          <t>50833; 62583</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>54911; 66725</t>
+          <t>64148; 73922</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>23123; 36215</t>
+          <t>19064; 31650</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>74976; 92392</t>
+          <t>72748; 91149</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>109227; 126402</t>
+          <t>109572; 125895</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>122314; 138188</t>
+          <t>123161; 138156</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>44981; 63194</t>
+          <t>46073; 64615</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>434</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>420</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>214</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>200999</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>304222</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>268476</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>162456</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>184301</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>299556</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>276814</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>180457</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>200999</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>304222</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>268476</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>179964</t>
+          <t>144687</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>360421</t>
+          <t>307143</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>171440; 198509</t>
+          <t>186230; 213697</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>284619; 312540</t>
+          <t>289252; 319160</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>263178; 289108</t>
+          <t>254378; 281816</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>163670; 205255</t>
+          <t>150383; 175572</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>188033; 215929</t>
+          <t>171439; 199853</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>287798; 318138</t>
+          <t>285815; 312603</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>254604; 282717</t>
+          <t>262174; 289089</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>164795; 193078</t>
+          <t>131478; 155723</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>366403; 403945</t>
+          <t>364768; 404199</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>582699; 623538</t>
+          <t>583210; 621768</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>526669; 564503</t>
+          <t>525292; 563262</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>339051; 388210</t>
+          <t>289848; 326240</t>
         </is>
       </c>
     </row>
